--- a/nr-update-patient-relationship-discr/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/nr-update-patient-relationship-discr/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5343" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6001" uniqueCount="743">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:02:57+00:00</t>
+    <t>2026-03-20T07:20:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1883,6 +1883,10 @@
     <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category').value}
+</t>
+  </si>
+  <si>
     <t>code</t>
   </si>
   <si>
@@ -1901,6 +1905,121 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0-ballot-2</t>
   </si>
   <si>
+    <t>Patient.contact.relationship:role.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category|2.2.0-ballot-2}
+</t>
+  </si>
+  <si>
+    <t>FR Core Patient Contact Relationship Category Extension</t>
+  </si>
+  <si>
+    <t>Catégorie de la relation du contact patient : indique si le CodeableConcept représente un rôle (ex : personne à prévenir) ou un type de relation (ex : mère)</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.url</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.url</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-relationship-category|2.2.0-ballot-2</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.text</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Patient.contact.relationship:relationType</t>
   </si>
   <si>
@@ -1911,6 +2030,33 @@
   </si>
   <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0-ballot-2</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.url</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.text</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -2515,11 +2661,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO143"/>
+  <dimension ref="A1:AO161"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.9765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.85546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.97265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2543,9 +2689,9 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.5625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.39453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="91.3359375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -16695,7 +16841,7 @@
         <v>82</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>142</v>
+        <v>590</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
@@ -16720,7 +16866,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16729,7 +16875,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16737,13 +16883,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>584</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16768,7 +16914,7 @@
         <v>277</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>586</v>
@@ -16804,7 +16950,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16837,7 +16983,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16846,7 +16992,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16854,14 +17000,12 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>82</v>
       </c>
@@ -16882,18 +17026,16 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>277</v>
+        <v>104</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>598</v>
+        <v>105</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>586</v>
+        <v>106</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>587</v>
-      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>82</v>
       </c>
@@ -16917,11 +17059,13 @@
         <v>82</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y123" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z123" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -16939,31 +17083,31 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>584</v>
+        <v>107</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>590</v>
+        <v>108</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16971,7 +17115,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>600</v>
@@ -16982,10 +17126,10 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>82</v>
@@ -16997,18 +17141,16 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>394</v>
+        <v>111</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>601</v>
+        <v>196</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>602</v>
+        <v>197</v>
       </c>
       <c r="N124" s="2"/>
-      <c r="O124" t="s" s="2">
-        <v>603</v>
-      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17044,43 +17186,43 @@
         <v>82</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>600</v>
+        <v>118</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17088,21 +17230,23 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C125" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="D125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>82</v>
@@ -17114,20 +17258,16 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>492</v>
+        <v>603</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17175,7 +17315,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>605</v>
+        <v>118</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17187,19 +17327,19 @@
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17207,10 +17347,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17233,18 +17373,16 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>611</v>
+        <v>104</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>612</v>
+        <v>105</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>613</v>
+        <v>106</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" t="s" s="2">
-        <v>614</v>
-      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17292,7 +17430,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>610</v>
+        <v>107</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17304,19 +17442,19 @@
         <v>82</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>532</v>
+        <v>108</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17324,10 +17462,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17338,7 +17476,7 @@
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>82</v>
@@ -17350,18 +17488,16 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>617</v>
+        <v>196</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>618</v>
+        <v>197</v>
       </c>
       <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>619</v>
-      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
@@ -17385,55 +17521,55 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>616</v>
+        <v>118</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17441,10 +17577,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17452,7 +17588,7 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>90</v>
@@ -17467,24 +17603,24 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>310</v>
+        <v>132</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>624</v>
+        <v>231</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>82</v>
+        <v>612</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>82</v>
@@ -17526,31 +17662,31 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>623</v>
+        <v>235</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>628</v>
+        <v>194</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17558,10 +17694,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17584,13 +17720,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>303</v>
+        <v>171</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>631</v>
+        <v>239</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17602,7 +17738,7 @@
         <v>82</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>82</v>
@@ -17617,13 +17753,11 @@
         <v>82</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>82</v>
@@ -17641,7 +17775,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>630</v>
+        <v>241</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17656,10 +17790,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>633</v>
+        <v>194</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17673,10 +17807,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17696,22 +17830,22 @@
         <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>560</v>
+        <v>149</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17760,7 +17894,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17775,16 +17909,16 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>639</v>
+        <v>624</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>640</v>
+        <v>82</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -17792,10 +17926,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>641</v>
+        <v>626</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17815,19 +17949,23 @@
         <v>82</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>105</v>
+        <v>628</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+        <v>629</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -17875,7 +18013,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>107</v>
+        <v>632</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -17887,10 +18025,10 @@
         <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>108</v>
+        <v>633</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>82</v>
@@ -17899,7 +18037,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -17907,21 +18045,23 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C132" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="D132" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>82</v>
@@ -17933,18 +18073,18 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>112</v>
+        <v>637</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
@@ -17968,13 +18108,11 @@
         <v>82</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>82</v>
+        <v>638</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>82</v>
@@ -17992,7 +18130,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>118</v>
+        <v>584</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18004,19 +18142,19 @@
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL132" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL132" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18024,46 +18162,42 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>643</v>
+        <v>598</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>581</v>
+        <v>105</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18111,22 +18245,22 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>583</v>
+        <v>107</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
@@ -18143,10 +18277,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>644</v>
+        <v>600</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18157,7 +18291,7 @@
         <v>90</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18169,20 +18303,16 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>645</v>
+        <v>196</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
@@ -18206,55 +18336,55 @@
         <v>82</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>644</v>
+        <v>118</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>649</v>
+        <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>651</v>
+        <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18262,18 +18392,20 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C135" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="D135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>90</v>
@@ -18288,20 +18420,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>385</v>
+        <v>603</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>653</v>
+        <v>604</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>656</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
       </c>
@@ -18349,31 +18477,31 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>652</v>
+        <v>118</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>659</v>
+        <v>82</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18381,21 +18509,21 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>607</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>661</v>
+        <v>82</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18407,17 +18535,15 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>662</v>
+        <v>104</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>663</v>
+        <v>105</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18466,31 +18592,31 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>660</v>
+        <v>107</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>666</v>
+        <v>108</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>667</v>
+        <v>82</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18498,10 +18624,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>668</v>
+        <v>643</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>668</v>
+        <v>609</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18512,7 +18638,7 @@
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>82</v>
@@ -18521,23 +18647,19 @@
         <v>82</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>669</v>
+        <v>111</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>670</v>
+        <v>196</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>673</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -18573,37 +18695,37 @@
         <v>82</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>668</v>
+        <v>118</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>674</v>
+        <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -18617,10 +18739,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>675</v>
+        <v>611</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18628,41 +18750,39 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>560</v>
+        <v>132</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>676</v>
+        <v>231</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>677</v>
+        <v>232</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>679</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q138" s="2"/>
       <c r="R138" t="s" s="2">
-        <v>82</v>
+        <v>612</v>
       </c>
       <c r="S138" t="s" s="2">
         <v>82</v>
@@ -18704,25 +18824,25 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>680</v>
+        <v>194</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>82</v>
@@ -18736,10 +18856,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>681</v>
+        <v>645</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>681</v>
+        <v>614</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18762,13 +18882,13 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>105</v>
+        <v>239</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>106</v>
+        <v>615</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18780,7 +18900,7 @@
         <v>82</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>82</v>
+        <v>636</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>82</v>
@@ -18795,13 +18915,11 @@
         <v>82</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -18819,7 +18937,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -18831,10 +18949,10 @@
         <v>82</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -18851,14 +18969,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>682</v>
+        <v>646</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>682</v>
+        <v>618</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18874,21 +18992,23 @@
         <v>82</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>112</v>
+        <v>619</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>113</v>
+        <v>620</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O140" s="2"/>
+        <v>621</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
       </c>
@@ -18936,7 +19056,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>118</v>
+        <v>623</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18948,10 +19068,10 @@
         <v>82</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>108</v>
+        <v>624</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -18960,7 +19080,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -18968,45 +19088,45 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>683</v>
+        <v>647</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>683</v>
+        <v>627</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J141" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>582</v>
+        <v>629</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>114</v>
+        <v>630</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>251</v>
+        <v>631</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19055,22 +19175,22 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>583</v>
+        <v>632</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>194</v>
+        <v>633</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
@@ -19079,7 +19199,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19087,10 +19207,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>684</v>
+        <v>648</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>684</v>
+        <v>648</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19098,7 +19218,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>90</v>
@@ -19110,21 +19230,21 @@
         <v>82</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>685</v>
+        <v>394</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>686</v>
+        <v>649</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19172,10 +19292,10 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>684</v>
+        <v>648</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>90</v>
@@ -19187,7 +19307,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>
@@ -19196,7 +19316,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>689</v>
+        <v>652</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19204,10 +19324,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>690</v>
+        <v>653</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>690</v>
+        <v>653</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19215,10 +19335,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>82</v>
@@ -19227,19 +19347,23 @@
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>171</v>
+        <v>492</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>691</v>
+        <v>654</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19263,13 +19387,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>692</v>
+        <v>82</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>693</v>
+        <v>82</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19287,13 +19411,13 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>690</v>
+        <v>653</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>82</v>
@@ -19302,7 +19426,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>694</v>
+        <v>497</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>108</v>
@@ -19311,9 +19435,2121 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AO143" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="P146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N149" s="2"/>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O150" s="2"/>
+      <c r="P150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="P151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="P152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="P153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O158" s="2"/>
+      <c r="P158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="P159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
+      <c r="P161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO161" t="s" s="2">
         <v>82</v>
       </c>
     </row>
